--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
@@ -450,7 +450,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,7 +459,16 @@
         </is>
       </c>
       <c r="C5">
-        <v>18.73</v>
+        <v>17.26</v>
+      </c>
+      <c r="D5">
+        <v>18.45</v>
+      </c>
+      <c r="E5">
+        <v>-1.189999999999998</v>
+      </c>
+      <c r="F5">
+        <v>-6.449864498644975</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -468,7 +477,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -477,7 +486,16 @@
         </is>
       </c>
       <c r="C6">
-        <v>10.59</v>
+        <v>10.55</v>
+      </c>
+      <c r="D6">
+        <v>11.76</v>
+      </c>
+      <c r="E6">
+        <v>-1.209999999999999</v>
+      </c>
+      <c r="F6">
+        <v>-10.28911564625849</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -486,7 +504,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -495,7 +513,16 @@
         </is>
       </c>
       <c r="C7">
-        <v>13.78</v>
+        <v>13.35</v>
+      </c>
+      <c r="D7">
+        <v>14.5</v>
+      </c>
+      <c r="E7">
+        <v>-1.15</v>
+      </c>
+      <c r="F7">
+        <v>-7.931034482758625</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -562,7 +589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -590,20 +617,10 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B3">
-        <v>13.78</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="B4">
         <v>12.83</v>
       </c>
     </row>
@@ -696,7 +713,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -705,7 +722,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>13.78</v>
+        <v>12.83</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -714,7 +731,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -723,7 +740,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>12.99</v>
+        <v>12.45</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -732,7 +749,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bíobío</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -741,7 +758,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>12.66</v>
+        <v>11.57</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -750,7 +767,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -759,7 +776,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>12.83</v>
+        <v>13.35</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -768,7 +785,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,7 +794,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>12.45</v>
+        <v>12.86</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -786,7 +803,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -795,7 +812,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>11.57</v>
+        <v>11.77</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,7 +408,7 @@
         <v>16.33</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -426,7 +426,7 @@
         <v>10.23</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +444,7 @@
         <v>12.83</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -471,7 +471,7 @@
         <v>-6.449864498644975</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>-10.28911564625849</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>-7.931034482758625</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>20.02</v>
+        <v>18.73</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -558,27 +558,81 @@
         </is>
       </c>
       <c r="C9">
-        <v>12.73</v>
+        <v>10.59</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>13.78</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Arauco</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>20.02</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>12.73</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Arauco</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C13">
         <v>15.92</v>
       </c>
-      <c r="G10">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
@@ -589,7 +643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -617,10 +671,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Concepción</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>12.83</v>
       </c>
     </row>
@@ -631,7 +695,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -713,7 +777,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,7 +786,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>12.83</v>
+        <v>13.78</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -731,7 +795,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -740,7 +804,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>12.45</v>
+        <v>12.99</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -749,7 +813,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -758,7 +822,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>11.57</v>
+        <v>12.66</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -767,7 +831,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -776,7 +840,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>13.35</v>
+        <v>12.83</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -785,7 +849,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Promedio Regional</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -794,7 +858,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>12.86</v>
+        <v>12.45</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -803,18 +867,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>11.57</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Promedio Regional</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>13.35</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>12.86</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C13">
         <v>11.77</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D13" t="b">
         <v>0</v>
       </c>
     </row>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:15</t>
+    <t xml:space="preserve">2026-08-19 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -83,13 +83,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_peringr_median_a_2022_biobio.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -779,23 +785,23 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -818,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -867,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -878,7 +884,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>15.92</v>
@@ -889,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>15.41</v>
@@ -900,7 +906,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>10.74</v>
@@ -911,7 +917,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>13.78</v>
@@ -922,7 +928,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>12.99</v>
@@ -933,7 +939,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>12.66</v>
@@ -944,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>12.83</v>
@@ -955,7 +961,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>12.45</v>
@@ -966,7 +972,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>11.57</v>
@@ -977,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>13.35</v>
@@ -988,7 +994,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>12.86</v>
@@ -999,7 +1005,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>11.77</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2022_biobio.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:50</t>
+    <t xml:space="preserve">2026-09-07 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
